--- a/仕様/2Dアクション仕様.xlsx
+++ b/仕様/2Dアクション仕様.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="207">
   <si>
     <r>
       <rPr>
@@ -1409,6 +1409,42 @@
   </si>
   <si>
     <t xml:space="preserve">敵を倒したりマップに落ちている宝箱などからお金が入手可能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◆UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要なUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCのHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面上部に横長の長方形で表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダメージを受けるとゲージの左側から色が削れ、全部色がなくなる＝0になると死亡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボスのHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCのHPの下に表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC同様に左から削れていき、全部色がなくなれば撃破</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">経験値がたまりレベルが上がった時に</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCの上部に「LevelUp！！」の文字をポップさせる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGptによる、ゲーム画面のイメージ</t>
   </si>
   <si>
     <t xml:space="preserve">◆エフェクト</t>
@@ -2153,6 +2189,49 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>781920</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>7560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>41400</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>108360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="画像 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="781920" y="20400120"/>
+          <a:ext cx="3979440" cy="2539080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -2264,11 +2343,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:F168"/>
+  <dimension ref="A2:F193"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.96"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2942,384 +3021,447 @@
         <v>116</v>
       </c>
     </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
-        <v>117</v>
+      <c r="C116" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C118" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D119" s="1" t="s">
-        <v>120</v>
-      </c>
+      <c r="E117" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C118" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E119" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C120" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="D120" s="1" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F121" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D123" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F123" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D125" s="3" t="s">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E121" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B142" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C143" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D144" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D145" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F146" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D148" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D150" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D126" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D127" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D128" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C130" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D131" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D132" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C133" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D134" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F134" s="1" t="s">
+    <row r="151" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D151" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D135" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F135" s="1" t="s">
+      <c r="E151" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C138" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D139" s="1" t="s">
+    <row r="152" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D152" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E139" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F139" s="1" t="s">
+      <c r="E152" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F140" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C142" s="1" t="s">
+    <row r="153" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D153" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D143" s="1" t="s">
+      <c r="E153" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E143" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D144" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F144" s="1" t="s">
+    </row>
+    <row r="155" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C155" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D156" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="2" t="s">
+      <c r="E156" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C148" s="1" t="s">
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D157" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D148" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E148" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F148" s="0" t="s">
+      <c r="E157" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F157" s="1" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D149" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E149" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F149" s="0" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D150" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E150" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F150" s="0" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C152" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D152" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="E152" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F152" s="0" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D153" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="E153" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F153" s="0" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C155" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D155" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="E155" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F155" s="0" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D156" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="E156" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F156" s="0" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C158" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D158" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="E158" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F158" s="0" t="s">
-        <v>161</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D159" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="0" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C161" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D161" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="E161" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F161" s="0" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D162" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="E162" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F162" s="0" t="s">
-        <v>167</v>
+      <c r="D160" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C163" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C164" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D164" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="E164" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F164" s="0" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="0" t="s">
-        <v>170</v>
+      <c r="D164" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F165" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C167" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D168" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D169" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B172" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C173" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D174" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D175" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C177" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D178" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C180" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F180" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D167" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="E167" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F167" s="0" t="s">
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D181" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C183" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C168" s="1" t="s">
+      <c r="E183" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D168" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="E168" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F168" s="0" t="s">
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B185" s="1" t="s">
         <v>174</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C186" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D187" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C189" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B191" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C192" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C193" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -3330,6 +3472,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3348,15 +3491,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3364,7 +3507,7 @@
         <v>46160</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3372,7 +3515,7 @@
         <v>46161</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3380,7 +3523,7 @@
         <v>46162</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3388,10 +3531,10 @@
         <v>46163</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3399,10 +3542,10 @@
         <v>46164</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3410,10 +3553,10 @@
         <v>46165</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3421,10 +3564,10 @@
         <v>46166</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3432,7 +3575,7 @@
         <v>46167</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3440,7 +3583,7 @@
         <v>46168</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3448,10 +3591,10 @@
         <v>46169</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3459,10 +3602,10 @@
         <v>46170</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3470,10 +3613,10 @@
         <v>46171</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3481,10 +3624,10 @@
         <v>46172</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3492,10 +3635,10 @@
         <v>46173</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3503,10 +3646,10 @@
         <v>46174</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3514,7 +3657,7 @@
         <v>46175</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3522,7 +3665,7 @@
         <v>46176</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
